--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/23.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/23.xlsx
@@ -426,13 +426,13 @@
         <v>-13.07509212610798</v>
       </c>
       <c r="E2">
-        <v>-8.407825042366825</v>
+        <v>-10.63961552993705</v>
       </c>
       <c r="F2">
-        <v>-5.793862698159132</v>
+        <v>-5.279579079805087</v>
       </c>
       <c r="G2">
-        <v>-7.115479168408849</v>
+        <v>-7.966872028016456</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.10146324804945</v>
       </c>
       <c r="E3">
-        <v>-8.78956634426542</v>
+        <v>-11.1320916067452</v>
       </c>
       <c r="F3">
-        <v>-5.529457763594364</v>
+        <v>-5.18824826017683</v>
       </c>
       <c r="G3">
-        <v>-7.022234342749737</v>
+        <v>-8.041614214656581</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.40400761776224</v>
       </c>
       <c r="E4">
-        <v>-9.763903754807759</v>
+        <v>-10.78638790099965</v>
       </c>
       <c r="F4">
-        <v>-5.717753957924719</v>
+        <v>-4.804332275307968</v>
       </c>
       <c r="G4">
-        <v>-6.851211560190987</v>
+        <v>-7.899002533915858</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.75636595262161</v>
       </c>
       <c r="E5">
-        <v>-10.22865198526695</v>
+        <v>-11.6789048431714</v>
       </c>
       <c r="F5">
-        <v>-5.647456215020944</v>
+        <v>-4.830125151128937</v>
       </c>
       <c r="G5">
-        <v>-6.679414109976048</v>
+        <v>-7.325304855233396</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.09777363129528</v>
       </c>
       <c r="E6">
-        <v>-10.08193848436645</v>
+        <v>-12.6999806339469</v>
       </c>
       <c r="F6">
-        <v>-5.629547740139822</v>
+        <v>-4.782749162628027</v>
       </c>
       <c r="G6">
-        <v>-7.307315350772996</v>
+        <v>-7.899475941927974</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.2987971853615</v>
       </c>
       <c r="E7">
-        <v>-10.85368102475363</v>
+        <v>-13.0161315183184</v>
       </c>
       <c r="F7">
-        <v>-5.317622681146057</v>
+        <v>-4.740810577759094</v>
       </c>
       <c r="G7">
-        <v>-6.457905507943414</v>
+        <v>-7.839515341120694</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.26440944547269</v>
       </c>
       <c r="E8">
-        <v>-11.62905087282096</v>
+        <v>-12.8059514542004</v>
       </c>
       <c r="F8">
-        <v>-5.303029332610938</v>
+        <v>-4.760323600299439</v>
       </c>
       <c r="G8">
-        <v>-6.612143824618058</v>
+        <v>-7.217394312835313</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.88989058753596</v>
       </c>
       <c r="E9">
-        <v>-12.6496194745076</v>
+        <v>-14.14677373770949</v>
       </c>
       <c r="F9">
-        <v>-4.859962944977775</v>
+        <v>-4.484055616159178</v>
       </c>
       <c r="G9">
-        <v>-6.716406145831865</v>
+        <v>-8.210081256059015</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.10122645124421</v>
       </c>
       <c r="E10">
-        <v>-12.84095655827969</v>
+        <v>-14.56694367003718</v>
       </c>
       <c r="F10">
-        <v>-4.750159532267089</v>
+        <v>-4.370039126837855</v>
       </c>
       <c r="G10">
-        <v>-6.714131801046386</v>
+        <v>-7.546734004173089</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-20.84242357434207</v>
       </c>
       <c r="E11">
-        <v>-13.20283597318064</v>
+        <v>-15.543337007779</v>
       </c>
       <c r="F11">
-        <v>-4.902948586243847</v>
+        <v>-4.105065932234766</v>
       </c>
       <c r="G11">
-        <v>-6.262470762578078</v>
+        <v>-8.100565099074384</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-20.0963227519714</v>
       </c>
       <c r="E12">
-        <v>-13.62020730857159</v>
+        <v>-15.02647056996553</v>
       </c>
       <c r="F12">
-        <v>-4.706817693017814</v>
+        <v>-3.847861167135131</v>
       </c>
       <c r="G12">
-        <v>-5.428398677231939</v>
+        <v>-7.026031538483281</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.87491410196253</v>
       </c>
       <c r="E13">
-        <v>-14.8658093691214</v>
+        <v>-16.416517365938</v>
       </c>
       <c r="F13">
-        <v>-4.740044337911504</v>
+        <v>-3.913723002596913</v>
       </c>
       <c r="G13">
-        <v>-5.718723589389404</v>
+        <v>-6.911943518108917</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.23325048864122</v>
       </c>
       <c r="E14">
-        <v>-16.11824036847477</v>
+        <v>-16.80483854056974</v>
       </c>
       <c r="F14">
-        <v>-4.257952733565054</v>
+        <v>-3.436749880432361</v>
       </c>
       <c r="G14">
-        <v>-5.43838328257838</v>
+        <v>-6.604648749517148</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.25708263833725</v>
       </c>
       <c r="E15">
-        <v>-15.09556602637456</v>
+        <v>-15.80040942024643</v>
       </c>
       <c r="F15">
-        <v>-4.108697494928639</v>
+        <v>-3.186460326411296</v>
       </c>
       <c r="G15">
-        <v>-5.123894698529774</v>
+        <v>-6.680883992195485</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.06290684012853</v>
       </c>
       <c r="E16">
-        <v>-15.65300759129676</v>
+        <v>-17.20088076338456</v>
       </c>
       <c r="F16">
-        <v>-3.763794301262023</v>
+        <v>-3.217112405417086</v>
       </c>
       <c r="G16">
-        <v>-4.657250130950725</v>
+        <v>-6.437191424504194</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.78757162870897</v>
       </c>
       <c r="E17">
-        <v>-16.47315046187792</v>
+        <v>-17.99348145505107</v>
       </c>
       <c r="F17">
-        <v>-3.65263070927594</v>
+        <v>-2.821799741820509</v>
       </c>
       <c r="G17">
-        <v>-3.754653063487211</v>
+        <v>-5.432930814075201</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.574254508534006</v>
       </c>
       <c r="E18">
-        <v>-16.8052279893344</v>
+        <v>-18.79703199686813</v>
       </c>
       <c r="F18">
-        <v>-3.091721603287922</v>
+        <v>-2.148018950261836</v>
       </c>
       <c r="G18">
-        <v>-3.591688148771048</v>
+        <v>-5.516015575474289</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.565346981280372</v>
       </c>
       <c r="E19">
-        <v>-18.94775772573943</v>
+        <v>-18.68776897601106</v>
       </c>
       <c r="F19">
-        <v>-3.029650377061349</v>
+        <v>-1.831663782397899</v>
       </c>
       <c r="G19">
-        <v>-3.13512419235908</v>
+        <v>-5.73413748942025</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.87978701052648</v>
       </c>
       <c r="E20">
-        <v>-19.61112482617504</v>
+        <v>-19.91316045706463</v>
       </c>
       <c r="F20">
-        <v>-2.436427487057526</v>
+        <v>-1.772481901672291</v>
       </c>
       <c r="G20">
-        <v>-4.111658983896677</v>
+        <v>-6.226432163837572</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.603625301276647</v>
       </c>
       <c r="E21">
-        <v>-19.13525919202702</v>
+        <v>-21.19332835971499</v>
       </c>
       <c r="F21">
-        <v>-2.214830094767227</v>
+        <v>-1.025684665393856</v>
       </c>
       <c r="G21">
-        <v>-4.189820964078869</v>
+        <v>-6.011839291436474</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.778309920912553</v>
       </c>
       <c r="E22">
-        <v>-19.18821516707272</v>
+        <v>-21.32870256170029</v>
       </c>
       <c r="F22">
-        <v>-2.203975168320942</v>
+        <v>-0.9285279378217099</v>
       </c>
       <c r="G22">
-        <v>-3.788347795985914</v>
+        <v>-5.656823008896111</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.40496537123995</v>
       </c>
       <c r="E23">
-        <v>-19.78194792269239</v>
+        <v>-21.54749125490687</v>
       </c>
       <c r="F23">
-        <v>-2.519029799362484</v>
+        <v>-0.9306046549005283</v>
       </c>
       <c r="G23">
-        <v>-4.009495548554768</v>
+        <v>-5.812852330707501</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.448655525295609</v>
       </c>
       <c r="E24">
-        <v>-20.50674830151605</v>
+        <v>-22.01457164948002</v>
       </c>
       <c r="F24">
-        <v>-1.442708010250405</v>
+        <v>-0.5338514603904827</v>
       </c>
       <c r="G24">
-        <v>-4.330327137856617</v>
+        <v>-5.545793932600033</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.841335558156971</v>
       </c>
       <c r="E25">
-        <v>-20.77039605824262</v>
+        <v>-22.0075344008721</v>
       </c>
       <c r="F25">
-        <v>-1.626870651240791</v>
+        <v>-0.7984245535380197</v>
       </c>
       <c r="G25">
-        <v>-4.152408488939566</v>
+        <v>-6.45941842725486</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.497768233572923</v>
       </c>
       <c r="E26">
-        <v>-21.98347008999534</v>
+        <v>-22.10788538488207</v>
       </c>
       <c r="F26">
-        <v>-1.74437125385829</v>
+        <v>-0.5885353061188893</v>
       </c>
       <c r="G26">
-        <v>-4.429706404399999</v>
+        <v>-6.117852891240555</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.328159121175632</v>
       </c>
       <c r="E27">
-        <v>-21.0557170915699</v>
+        <v>-22.06900390705221</v>
       </c>
       <c r="F27">
-        <v>-1.510840400763262</v>
+        <v>-0.5444139731435792</v>
       </c>
       <c r="G27">
-        <v>-5.787576315515166</v>
+        <v>-6.300283813727634</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.254045013333551</v>
       </c>
       <c r="E28">
-        <v>-21.46002377944872</v>
+        <v>-22.70219325670071</v>
       </c>
       <c r="F28">
-        <v>-1.243772264998493</v>
+        <v>-0.8099786220722671</v>
       </c>
       <c r="G28">
-        <v>-5.761323689388745</v>
+        <v>-6.424826536915016</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.21102535726691</v>
       </c>
       <c r="E29">
-        <v>-21.99336027722809</v>
+        <v>-21.96811856310934</v>
       </c>
       <c r="F29">
-        <v>-1.484199276721827</v>
+        <v>-0.6966090876925296</v>
       </c>
       <c r="G29">
-        <v>-4.654581831246073</v>
+        <v>-5.784451160526094</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.149268117440815</v>
       </c>
       <c r="E30">
-        <v>-21.54855091782467</v>
+        <v>-22.95439303113589</v>
       </c>
       <c r="F30">
-        <v>-1.649258937036253</v>
+        <v>-0.6758145807800536</v>
       </c>
       <c r="G30">
-        <v>-5.350832595246814</v>
+        <v>-6.691550569923017</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.027870192900352</v>
       </c>
       <c r="E31">
-        <v>-21.15517596620037</v>
+        <v>-22.50852853728868</v>
       </c>
       <c r="F31">
-        <v>-1.798896053045359</v>
+        <v>-1.145694392874434</v>
       </c>
       <c r="G31">
-        <v>-5.514989306357116</v>
+        <v>-5.913433325281638</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.815088437390463</v>
       </c>
       <c r="E32">
-        <v>-20.91890283485017</v>
+        <v>-22.30932549416527</v>
       </c>
       <c r="F32">
-        <v>-1.937867110376018</v>
+        <v>-1.368742256487034</v>
       </c>
       <c r="G32">
-        <v>-5.64015441210588</v>
+        <v>-6.182835589630909</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.489046289565218</v>
       </c>
       <c r="E33">
-        <v>-20.196171968648</v>
+        <v>-22.05572189278772</v>
       </c>
       <c r="F33">
-        <v>-2.120948731905751</v>
+        <v>-1.173500201484205</v>
       </c>
       <c r="G33">
-        <v>-5.177648026450921</v>
+        <v>-5.513992832149794</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.03479110376829</v>
       </c>
       <c r="E34">
-        <v>-19.62735940549254</v>
+        <v>-21.41993772753282</v>
       </c>
       <c r="F34">
-        <v>-2.137965883461461</v>
+        <v>-1.15125025304501</v>
       </c>
       <c r="G34">
-        <v>-4.667694902127126</v>
+        <v>-5.088786363085804</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.44506263540522</v>
       </c>
       <c r="E35">
-        <v>-19.08111222831731</v>
+        <v>-20.67803330238218</v>
       </c>
       <c r="F35">
-        <v>-1.769323336765417</v>
+        <v>-1.340398009065444</v>
       </c>
       <c r="G35">
-        <v>-5.279394333054881</v>
+        <v>-5.294510283987194</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.71720626747652</v>
       </c>
       <c r="E36">
-        <v>-19.62359624359217</v>
+        <v>-21.25574884543672</v>
       </c>
       <c r="F36">
-        <v>-1.793527403907815</v>
+        <v>-1.452514223564746</v>
       </c>
       <c r="G36">
-        <v>-3.580435604483065</v>
+        <v>-5.319471797353298</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.8527899089915</v>
       </c>
       <c r="E37">
-        <v>-19.98031319812438</v>
+        <v>-20.71551548174367</v>
       </c>
       <c r="F37">
-        <v>-2.099749153333306</v>
+        <v>-1.452615284387887</v>
       </c>
       <c r="G37">
-        <v>-4.859425147034017</v>
+        <v>-4.905696642036411</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.85519434648817</v>
       </c>
       <c r="E38">
-        <v>-19.57881869260432</v>
+        <v>-20.59220966298881</v>
       </c>
       <c r="F38">
-        <v>-1.537218103970606</v>
+        <v>-1.441942598770218</v>
       </c>
       <c r="G38">
-        <v>-3.684923042793542</v>
+        <v>-4.376376826307879</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.72761341451684</v>
       </c>
       <c r="E39">
-        <v>-18.65254197670539</v>
+        <v>-20.38846456043571</v>
       </c>
       <c r="F39">
-        <v>-1.818212752511241</v>
+        <v>-1.556292920154871</v>
       </c>
       <c r="G39">
-        <v>-4.417848030278329</v>
+        <v>-3.837883488890028</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.47363738343781</v>
       </c>
       <c r="E40">
-        <v>-18.14418907002634</v>
+        <v>-20.40803209662285</v>
       </c>
       <c r="F40">
-        <v>-2.393643139070334</v>
+        <v>-1.5139881968939</v>
       </c>
       <c r="G40">
-        <v>-2.885562027426661</v>
+        <v>-4.000173052316181</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.09610258132525</v>
       </c>
       <c r="E41">
-        <v>-17.93099757069323</v>
+        <v>-20.52457237521025</v>
       </c>
       <c r="F41">
-        <v>-1.75338720467036</v>
+        <v>-1.540994630959969</v>
       </c>
       <c r="G41">
-        <v>-2.688955348940424</v>
+        <v>-3.584216247488913</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.599298953860066</v>
       </c>
       <c r="E42">
-        <v>-17.60270584750717</v>
+        <v>-19.5065397189679</v>
       </c>
       <c r="F42">
-        <v>-2.336619155429019</v>
+        <v>-1.788794112568219</v>
       </c>
       <c r="G42">
-        <v>-3.246192995201628</v>
+        <v>-3.379713917891514</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.993587425819666</v>
       </c>
       <c r="E43">
-        <v>-16.72720238218224</v>
+        <v>-18.87068762660289</v>
       </c>
       <c r="F43">
-        <v>-2.298065279767924</v>
+        <v>-1.635181661393079</v>
       </c>
       <c r="G43">
-        <v>-2.898645303397861</v>
+        <v>-3.189006631556258</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.294723181077099</v>
       </c>
       <c r="E44">
-        <v>-17.04596619605616</v>
+        <v>-18.48957125411735</v>
       </c>
       <c r="F44">
-        <v>-1.980798079393505</v>
+        <v>-1.848701643138679</v>
       </c>
       <c r="G44">
-        <v>-2.562816942803113</v>
+        <v>-3.890627100421697</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.526644260732704</v>
       </c>
       <c r="E45">
-        <v>-17.11475824470668</v>
+        <v>-18.20410078114782</v>
       </c>
       <c r="F45">
-        <v>-2.776871578994872</v>
+        <v>-1.960749103143549</v>
       </c>
       <c r="G45">
-        <v>-2.388801427076862</v>
+        <v>-3.627819442786654</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.720196989680077</v>
       </c>
       <c r="E46">
-        <v>-16.42283005870469</v>
+        <v>-18.04277842309857</v>
       </c>
       <c r="F46">
-        <v>-2.444547144339766</v>
+        <v>-1.772168778794033</v>
       </c>
       <c r="G46">
-        <v>-2.43914158254702</v>
+        <v>-3.466248267742523</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.914511543684119</v>
       </c>
       <c r="E47">
-        <v>-15.74161624220485</v>
+        <v>-18.02356410788402</v>
       </c>
       <c r="F47">
-        <v>-2.584080663136926</v>
+        <v>-2.189508559998452</v>
       </c>
       <c r="G47">
-        <v>-2.293778838463161</v>
+        <v>-3.448010472366679</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.155867857035963</v>
       </c>
       <c r="E48">
-        <v>-15.99638818987638</v>
+        <v>-17.18233213384914</v>
       </c>
       <c r="F48">
-        <v>-2.561132400977172</v>
+        <v>-2.439169383160792</v>
       </c>
       <c r="G48">
-        <v>-2.800113536512532</v>
+        <v>-2.641790006642427</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.489810764568943</v>
       </c>
       <c r="E49">
-        <v>-15.50091879174915</v>
+        <v>-17.63923251885304</v>
       </c>
       <c r="F49">
-        <v>-2.856452835381821</v>
+        <v>-2.365107538778696</v>
       </c>
       <c r="G49">
-        <v>-1.985282341840636</v>
+        <v>-3.12118017454767</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.957231034079703</v>
       </c>
       <c r="E50">
-        <v>-15.31976624602031</v>
+        <v>-17.29626401140812</v>
       </c>
       <c r="F50">
-        <v>-2.957185625031852</v>
+        <v>-2.451441646233267</v>
       </c>
       <c r="G50">
-        <v>-2.921537725801921</v>
+        <v>-2.636450096687583</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.587992751276454</v>
       </c>
       <c r="E51">
-        <v>-15.45314339096823</v>
+        <v>-16.08193559235528</v>
       </c>
       <c r="F51">
-        <v>-2.91988424088379</v>
+        <v>-2.660027043360391</v>
       </c>
       <c r="G51">
-        <v>-2.533601378419045</v>
+        <v>-2.907527497079725</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.400732393530133</v>
       </c>
       <c r="E52">
-        <v>-14.83325416948026</v>
+        <v>-16.64412752651153</v>
       </c>
       <c r="F52">
-        <v>-3.198465026812666</v>
+        <v>-2.405332231491238</v>
       </c>
       <c r="G52">
-        <v>-1.88914740992574</v>
+        <v>-3.139169679008069</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.398690190530322</v>
       </c>
       <c r="E53">
-        <v>-15.05250929550963</v>
+        <v>-16.36178622908129</v>
       </c>
       <c r="F53">
-        <v>-3.104490058434674</v>
+        <v>-2.349349505675242</v>
       </c>
       <c r="G53">
-        <v>-1.604036606992627</v>
+        <v>-3.072068231472582</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.56915305714522</v>
       </c>
       <c r="E54">
-        <v>-14.97440670429934</v>
+        <v>-16.1578690445159</v>
       </c>
       <c r="F54">
-        <v>-3.133180563430634</v>
+        <v>-2.698617367187208</v>
       </c>
       <c r="G54">
-        <v>-1.448871337566987</v>
+        <v>-3.296274928119723</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.886797798740831</v>
       </c>
       <c r="E55">
-        <v>-14.07516950670021</v>
+        <v>-16.18657051277651</v>
       </c>
       <c r="F55">
-        <v>-3.460312791204993</v>
+        <v>-2.583281288593225</v>
       </c>
       <c r="G55">
-        <v>-2.512582724790212</v>
+        <v>-2.891802405768187</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.318717561554873</v>
       </c>
       <c r="E56">
-        <v>-13.7718840169845</v>
+        <v>-15.91910978093549</v>
       </c>
       <c r="F56">
-        <v>-3.336138032423139</v>
+        <v>-2.967029114879318</v>
       </c>
       <c r="G56">
-        <v>-2.362528937677206</v>
+        <v>-2.934385953039832</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.831395509266473</v>
       </c>
       <c r="E57">
-        <v>-13.40394550386129</v>
+        <v>-15.44631445216466</v>
       </c>
       <c r="F57">
-        <v>-3.405367181377302</v>
+        <v>-2.799896879323087</v>
       </c>
       <c r="G57">
-        <v>-2.627849299376556</v>
+        <v>-3.063828283625336</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.390076840287624</v>
       </c>
       <c r="E58">
-        <v>-13.82902883048729</v>
+        <v>-15.67571788844523</v>
       </c>
       <c r="F58">
-        <v>-3.06575891214938</v>
+        <v>-2.906060445665872</v>
       </c>
       <c r="G58">
-        <v>-2.719422299538336</v>
+        <v>-2.928228338336788</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.961974945502501</v>
       </c>
       <c r="E59">
-        <v>-12.69897984119121</v>
+        <v>-15.23435016928764</v>
       </c>
       <c r="F59">
-        <v>-3.173769737800407</v>
+        <v>-2.754355724619379</v>
       </c>
       <c r="G59">
-        <v>-2.205238298015353</v>
+        <v>-3.068333936104284</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.516785131968512</v>
       </c>
       <c r="E60">
-        <v>-11.74402882787571</v>
+        <v>-14.99734342514819</v>
       </c>
       <c r="F60">
-        <v>-3.188205696528994</v>
+        <v>-2.849210419179145</v>
       </c>
       <c r="G60">
-        <v>-2.203182449235466</v>
+        <v>-2.922752696014833</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.030033202543589</v>
       </c>
       <c r="E61">
-        <v>-12.50126666601632</v>
+        <v>-14.47858861367352</v>
       </c>
       <c r="F61">
-        <v>-3.398885206450396</v>
+        <v>-3.276482325543129</v>
       </c>
       <c r="G61">
-        <v>-2.781240116393147</v>
+        <v>-3.731926168360115</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.483278241543376</v>
       </c>
       <c r="E62">
-        <v>-11.89100950874266</v>
+        <v>-14.94637997866587</v>
       </c>
       <c r="F62">
-        <v>-3.599652472029898</v>
+        <v>-3.090459171366056</v>
       </c>
       <c r="G62">
-        <v>-2.626849514623696</v>
+        <v>-3.255104983793347</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.863002311977078</v>
       </c>
       <c r="E63">
-        <v>-13.4052542328495</v>
+        <v>-15.22858542187587</v>
       </c>
       <c r="F63">
-        <v>-3.430609192875408</v>
+        <v>-3.109241573857132</v>
       </c>
       <c r="G63">
-        <v>-3.691921536063562</v>
+        <v>-3.665976790672294</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.164321847359385</v>
       </c>
       <c r="E64">
-        <v>-12.25078771170406</v>
+        <v>-14.01171200043072</v>
       </c>
       <c r="F64">
-        <v>-3.489462211742105</v>
+        <v>-3.320561411780897</v>
       </c>
       <c r="G64">
-        <v>-2.989933596643263</v>
+        <v>-3.237039336785544</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.388862255614731</v>
       </c>
       <c r="E65">
-        <v>-12.60749108081425</v>
+        <v>-14.77866341531779</v>
       </c>
       <c r="F65">
-        <v>-3.776545360693315</v>
+        <v>-3.136248007923201</v>
       </c>
       <c r="G65">
-        <v>-2.825531905163056</v>
+        <v>-3.217692508654043</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.545137740268069</v>
       </c>
       <c r="E66">
-        <v>-12.6804946102919</v>
+        <v>-14.82284320773662</v>
       </c>
       <c r="F66">
-        <v>-3.433257483462159</v>
+        <v>-3.369316632007467</v>
       </c>
       <c r="G66">
-        <v>-3.377876565117218</v>
+        <v>-3.127698638714495</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.6434064102615</v>
       </c>
       <c r="E67">
-        <v>-11.34670504691672</v>
+        <v>-14.46101360604975</v>
       </c>
       <c r="F67">
-        <v>-3.269908401834513</v>
+        <v>-3.212371658770865</v>
       </c>
       <c r="G67">
-        <v>-3.326576351440672</v>
+        <v>-3.232033791930165</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.693331308646796</v>
       </c>
       <c r="E68">
-        <v>-12.04839209440524</v>
+        <v>-14.04521365113947</v>
       </c>
       <c r="F68">
-        <v>-3.723065132801176</v>
+        <v>-3.331997852143947</v>
       </c>
       <c r="G68">
-        <v>-3.004884020298612</v>
+        <v>-3.871886102123883</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.703722124792929</v>
       </c>
       <c r="E69">
-        <v>-11.36825152624521</v>
+        <v>-13.55530974756767</v>
       </c>
       <c r="F69">
-        <v>-3.782166661888713</v>
+        <v>-3.325692319473837</v>
       </c>
       <c r="G69">
-        <v>-2.342410752435055</v>
+        <v>-3.192009296360377</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.680421751105687</v>
       </c>
       <c r="E70">
-        <v>-12.51040965503781</v>
+        <v>-14.24750964201012</v>
       </c>
       <c r="F70">
-        <v>-3.999199749789586</v>
+        <v>-3.517679718951067</v>
       </c>
       <c r="G70">
-        <v>-2.984686381963519</v>
+        <v>-3.534938777136861</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.631122487299031</v>
       </c>
       <c r="E71">
-        <v>-12.55256521957521</v>
+        <v>-14.54138949121189</v>
       </c>
       <c r="F71">
-        <v>-4.027437966183618</v>
+        <v>-3.754150447958631</v>
       </c>
       <c r="G71">
-        <v>-1.938398395913478</v>
+        <v>-2.824667852777307</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.563614468705993</v>
       </c>
       <c r="E72">
-        <v>-11.84458812169004</v>
+        <v>-14.01267203692035</v>
       </c>
       <c r="F72">
-        <v>-4.015640357632948</v>
+        <v>-3.785912539284172</v>
       </c>
       <c r="G72">
-        <v>-2.124225938123848</v>
+        <v>-2.657654140866614</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.484429729027916</v>
       </c>
       <c r="E73">
-        <v>-11.44610505138508</v>
+        <v>-13.67236174371793</v>
       </c>
       <c r="F73">
-        <v>-3.992953859572478</v>
+        <v>-3.557358517545163</v>
       </c>
       <c r="G73">
-        <v>-2.121117335862472</v>
+        <v>-3.214871923854584</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.398438524954239</v>
       </c>
       <c r="E74">
-        <v>-12.28587432831549</v>
+        <v>-14.09133163043358</v>
       </c>
       <c r="F74">
-        <v>-3.809486218833041</v>
+        <v>-3.678542870002912</v>
       </c>
       <c r="G74">
-        <v>-2.806400262491608</v>
+        <v>-2.434258527876595</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.307733030888878</v>
       </c>
       <c r="E75">
-        <v>-11.848106745994</v>
+        <v>-14.30098186309269</v>
       </c>
       <c r="F75">
-        <v>-4.196034755307999</v>
+        <v>-3.744210867492439</v>
       </c>
       <c r="G75">
-        <v>-1.928960030581016</v>
+        <v>-2.232543677623262</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.214063125336498</v>
       </c>
       <c r="E76">
-        <v>-12.36059867791606</v>
+        <v>-14.78738525625656</v>
       </c>
       <c r="F76">
-        <v>-4.335362010621862</v>
+        <v>-3.95707975245944</v>
       </c>
       <c r="G76">
-        <v>-2.434473713336648</v>
+        <v>-2.208618365010949</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.116723831864521</v>
       </c>
       <c r="E77">
-        <v>-13.97459662746386</v>
+        <v>-15.16256932779205</v>
       </c>
       <c r="F77">
-        <v>-4.191574825211327</v>
+        <v>-4.093975749446086</v>
       </c>
       <c r="G77">
-        <v>-2.279262096273457</v>
+        <v>-2.569457897154891</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.012884609467392</v>
       </c>
       <c r="E78">
-        <v>-12.84543974754728</v>
+        <v>-15.61397214535064</v>
       </c>
       <c r="F78">
-        <v>-4.281862730279459</v>
+        <v>-4.168503136308555</v>
       </c>
       <c r="G78">
-        <v>-2.53598166066178</v>
+        <v>-2.235019965686637</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.899506987687253</v>
       </c>
       <c r="E79">
-        <v>-14.2314426162309</v>
+        <v>-16.27436403836322</v>
       </c>
       <c r="F79">
-        <v>-4.662616008404432</v>
+        <v>-4.250703690423156</v>
       </c>
       <c r="G79">
-        <v>-2.147863233274244</v>
+        <v>-2.091408500193053</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.774512128480297</v>
       </c>
       <c r="E80">
-        <v>-14.78234959316003</v>
+        <v>-17.19042904537486</v>
       </c>
       <c r="F80">
-        <v>-4.86026944091681</v>
+        <v>-4.296264725944531</v>
       </c>
       <c r="G80">
-        <v>-1.572420897092587</v>
+        <v>-1.937504548617875</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.640400865746221</v>
       </c>
       <c r="E81">
-        <v>-14.42389370460888</v>
+        <v>-18.02323352928146</v>
       </c>
       <c r="F81">
-        <v>-4.574326125511852</v>
+        <v>-4.396015900222245</v>
       </c>
       <c r="G81">
-        <v>-1.882251543567439</v>
+        <v>-1.468893516988499</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.500761330262669</v>
       </c>
       <c r="E82">
-        <v>-16.7255268467994</v>
+        <v>-18.64586700601808</v>
       </c>
       <c r="F82">
-        <v>-4.698973053713302</v>
+        <v>-4.211300738174192</v>
       </c>
       <c r="G82">
-        <v>-1.969861820718711</v>
+        <v>-1.809273877699745</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.358570801313951</v>
       </c>
       <c r="E83">
-        <v>-18.08139724943598</v>
+        <v>-18.32503367952265</v>
       </c>
       <c r="F83">
-        <v>-4.637708657337056</v>
+        <v>-4.531945192449824</v>
       </c>
       <c r="G83">
-        <v>-1.926129514144939</v>
+        <v>-1.823072231507427</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.214265127284717</v>
       </c>
       <c r="E84">
-        <v>-17.44639651018441</v>
+        <v>-19.5993507937551</v>
       </c>
       <c r="F84">
-        <v>-4.996464639080688</v>
+        <v>-4.475073628410624</v>
       </c>
       <c r="G84">
-        <v>-1.611369465362113</v>
+        <v>-1.836582567853193</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.065363287130117</v>
       </c>
       <c r="E85">
-        <v>-18.83277977068468</v>
+        <v>-20.27985816830975</v>
       </c>
       <c r="F85">
-        <v>-5.360661337925908</v>
+        <v>-4.975593093999752</v>
       </c>
       <c r="G85">
-        <v>-1.262037389512678</v>
+        <v>-1.925659416678362</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.910797555366228</v>
       </c>
       <c r="E86">
-        <v>-18.95420174425234</v>
+        <v>-20.75340522376585</v>
       </c>
       <c r="F86">
-        <v>-5.633701174297459</v>
+        <v>-4.824184100116058</v>
       </c>
       <c r="G86">
-        <v>-1.842031725810833</v>
+        <v>-1.345853781475946</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.747919634020703</v>
       </c>
       <c r="E87">
-        <v>-20.96930022208153</v>
+        <v>-22.97658255377348</v>
       </c>
       <c r="F87">
-        <v>-5.544116553154304</v>
+        <v>-5.063254246033607</v>
       </c>
       <c r="G87">
-        <v>-2.073094562269805</v>
+        <v>-2.416484208876248</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.574562187826775</v>
       </c>
       <c r="E88">
-        <v>-22.34231089883714</v>
+        <v>-22.75572434794539</v>
       </c>
       <c r="F88">
-        <v>-5.373274060000933</v>
+        <v>-4.860516294402845</v>
       </c>
       <c r="G88">
-        <v>-1.512410638102219</v>
+        <v>-1.730638489505436</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.389494468965698</v>
       </c>
       <c r="E89">
-        <v>-23.83472837822701</v>
+        <v>-25.24577823664706</v>
       </c>
       <c r="F89">
-        <v>-5.851416836938239</v>
+        <v>-4.99943599295453</v>
       </c>
       <c r="G89">
-        <v>-2.029064306597498</v>
+        <v>-1.738636767528315</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.195856630866702</v>
       </c>
       <c r="E90">
-        <v>-25.0425946648709</v>
+        <v>-26.23908995328153</v>
       </c>
       <c r="F90">
-        <v>-5.345632268136916</v>
+        <v>-5.29977799055495</v>
       </c>
       <c r="G90">
-        <v>-1.946307289206797</v>
+        <v>-1.47011510829249</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.005212352148597</v>
       </c>
       <c r="E91">
-        <v>-26.51158634821909</v>
+        <v>-28.21300648848496</v>
       </c>
       <c r="F91">
-        <v>-5.683286418661634</v>
+        <v>-4.83901187662617</v>
       </c>
       <c r="G91">
-        <v>-1.666960146057555</v>
+        <v>-2.049212286749502</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.832904008331552</v>
       </c>
       <c r="E92">
-        <v>-28.10229435594544</v>
+        <v>-29.68142305563418</v>
       </c>
       <c r="F92">
-        <v>-5.561809652510698</v>
+        <v>-4.960247587862892</v>
       </c>
       <c r="G92">
-        <v>-2.331105239418444</v>
+        <v>-2.479348158121468</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.698415056291791</v>
       </c>
       <c r="E93">
-        <v>-30.96202569178927</v>
+        <v>-32.23127317937013</v>
       </c>
       <c r="F93">
-        <v>-5.478750081399395</v>
+        <v>-5.225943947208624</v>
       </c>
       <c r="G93">
-        <v>-2.439628232741293</v>
+        <v>-2.817189330404093</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.621360311727262</v>
       </c>
       <c r="E94">
-        <v>-32.84405496090307</v>
+        <v>-33.72689455412042</v>
       </c>
       <c r="F94">
-        <v>-5.914940191221919</v>
+        <v>-5.0167074533029</v>
       </c>
       <c r="G94">
-        <v>-2.41442836009636</v>
+        <v>-3.325516976868105</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.620210959352192</v>
       </c>
       <c r="E95">
-        <v>-33.57195055171098</v>
+        <v>-36.16031081840816</v>
       </c>
       <c r="F95">
-        <v>-5.354696264258349</v>
+        <v>-4.956815661713093</v>
       </c>
       <c r="G95">
-        <v>-3.308967559717289</v>
+        <v>-3.087372883500632</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.718013468399818</v>
       </c>
       <c r="E96">
-        <v>-37.43621516278029</v>
+        <v>-37.15343233913431</v>
       </c>
       <c r="F96">
-        <v>-5.815584976562743</v>
+        <v>-4.861296616496282</v>
       </c>
       <c r="G96">
-        <v>-3.104557925394989</v>
+        <v>-3.790221564761141</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.916604960172244</v>
       </c>
       <c r="E97">
-        <v>-38.37609994307228</v>
+        <v>-40.80640288147974</v>
       </c>
       <c r="F97">
-        <v>-5.664810512109594</v>
+        <v>-5.00260781173985</v>
       </c>
       <c r="G97">
-        <v>-4.039505643868261</v>
+        <v>-3.901800191616737</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.23410889243719</v>
       </c>
       <c r="E98">
-        <v>-41.63987305106547</v>
+        <v>-42.36138802199658</v>
       </c>
       <c r="F98">
-        <v>-5.487712188330282</v>
+        <v>-4.799993286852104</v>
       </c>
       <c r="G98">
-        <v>-4.542685392018707</v>
+        <v>-4.947177777643478</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.637505274569349</v>
       </c>
       <c r="E99">
-        <v>-43.837007127055</v>
+        <v>-44.44696314080714</v>
       </c>
       <c r="F99">
-        <v>-6.434502166666602</v>
+        <v>-4.897851641614421</v>
       </c>
       <c r="G99">
-        <v>-4.723934449748265</v>
+        <v>-5.034413963148814</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.152837904087071</v>
       </c>
       <c r="E100">
-        <v>-45.86939984711947</v>
+        <v>-46.65216242900432</v>
       </c>
       <c r="F100">
-        <v>-5.527294067938251</v>
+        <v>-4.924409928915576</v>
       </c>
       <c r="G100">
-        <v>-5.944492863531081</v>
+        <v>-5.20577111080703</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.697921795102587</v>
       </c>
       <c r="E101">
-        <v>-48.00754602068508</v>
+        <v>-48.50870318216595</v>
       </c>
       <c r="F101">
-        <v>-6.080998862624122</v>
+        <v>-4.656527507993856</v>
       </c>
       <c r="G101">
-        <v>-5.287670696903059</v>
+        <v>-4.983547430937912</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.357943038185557</v>
       </c>
       <c r="E102">
-        <v>-50.69548629869243</v>
+        <v>-50.86483424480177</v>
       </c>
       <c r="F102">
-        <v>-5.77885433755521</v>
+        <v>-4.65572399161314</v>
       </c>
       <c r="G102">
-        <v>-6.183749300199748</v>
+        <v>-6.201437545016074</v>
       </c>
     </row>
   </sheetData>
